--- a/VerveStacks_IND_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39AA57C8-3C2A-4033-9695-5B5A362FE08F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C98C0C-14DD-49BC-A336-2B85E49827AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1103" yWindow="1103" windowWidth="21600" windowHeight="12772" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>

--- a/VerveStacks_IND_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_IND_grids_kan60/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_IND_grids_kan60\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C98C0C-14DD-49BC-A336-2B85E49827AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2535447A-59E0-40A7-9B63-00894D9DBB4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3675" yWindow="3675" windowWidth="21600" windowHeight="12773" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="controller" sheetId="5" r:id="rId1"/>
